--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -1596,13 +1596,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1676,13 +1676,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>孙国奉</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2216,15 +2216,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2236,7 +2232,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2254,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2372,11 +2368,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2866,13 +2866,13 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -2908,13 +2908,13 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -2950,13 +2950,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -2992,15 +2992,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3012,7 +3008,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3034,11 +3030,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3072,13 +3072,13 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3156,15 +3156,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3176,7 +3172,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3198,11 +3194,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3312,15 +3312,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3332,7 +3328,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3350,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3392,11 +3388,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3764,11 +3764,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -3780,7 +3784,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3802,15 +3806,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -4722,14 +4722,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
@@ -4738,7 +4746,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4806,22 +4814,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4852,14 +4852,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
@@ -4868,7 +4876,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4890,22 +4898,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4936,20 +4936,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -4982,23 +4982,23 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5032,22 +5032,26 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
@@ -5056,7 +5060,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5078,26 +5082,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5128,22 +5128,26 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5152,7 +5156,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5174,20 +5178,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -5220,23 +5224,23 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>408.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5270,26 +5274,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5320,22 +5320,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5344,7 +5352,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5366,20 +5374,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -5458,20 +5466,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -5504,22 +5512,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5528,7 +5544,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5550,30 +5566,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5582,7 +5590,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5604,20 +5612,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -5650,27 +5658,27 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>360.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>720.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5704,20 +5712,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -5750,20 +5758,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5796,20 +5804,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -5842,30 +5850,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5896,20 +5896,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -6920,11 +6920,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6944,7 +6940,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -6982,7 +6978,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7020,7 +7016,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -7036,7 +7032,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7054,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -7072,7 +7068,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7662,11 +7662,15 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -7676,11 +7680,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7700,15 +7700,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -7718,7 +7714,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8092,15 +8092,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -8112,7 +8108,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8130,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8172,13 +8168,13 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -8214,11 +8210,15 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8294,20 +8294,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -8382,20 +8382,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -8428,20 +8428,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -8516,20 +8516,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -8562,20 +8562,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -8608,20 +8608,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -9049,7 +9049,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T10:04:40.973652</t>
+          <t>生成时间: 2026-06-12T14:44:15.747839</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +491,21 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>事件类型</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>增资后总股本(万股)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>认购占比</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -513,6 +531,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>35.00%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>2004年6月1日，孙国奉、孙国敏和张松满就设立三联有限签署了股东协议书及公司章程，注册资本500万元，孙国奉以机器设备出资175万元（35%）；孙国敏以货币和机器设备出资162.5万元（32.5%）；张松满以货币和机器设备出资162.5万元（32.5%）。2004年6月18日经芜湖市工商行政管理局核准。</t>
         </is>
       </c>
@@ -538,6 +566,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>32.50%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>2004年6月1日，孙国奉、孙国敏和张松满就设立三联有限签署了股东协议书及公司章程，注册资本500万元，孙国奉以机器设备出资175万元（35%）；孙国敏以货币和机器设备出资162.5万元（32.5%）；张松满以货币和机器设备出资162.5万元（32.5%）。2004年6月18日经芜湖市工商行政管理局核准。</t>
         </is>
       </c>
@@ -563,6 +601,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>32.50%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>2004年6月1日，孙国奉、孙国敏和张松满就设立三联有限签署了股东协议书及公司章程，注册资本500万元，孙国奉以机器设备出资175万元（35%）；孙国敏以货币和机器设备出资162.5万元（32.5%）；张松满以货币和机器设备出资162.5万元（32.5%）。2004年6月18日经芜湖市工商行政管理局核准。</t>
         </is>
       </c>
@@ -588,6 +636,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>2007年12月，三联有限第一次增资1,500万元，温州三联出资620万元，张爱连出资400万元，孙娟丽出资380万元，孙国奉出资100万元。注册资本增至2,000万元。2008年1月，温州三联将395万元转让予孙国奉、97.5万元予孙国敏、127.5万元予张松满；孙娟丽将380万元转让予张松满；张爱连将400万元转让予孙国敏。</t>
         </is>
       </c>
@@ -613,6 +666,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>2007年12月，三联有限第一次增资1,500万元，温州三联出资620万元，张爱连出资400万元，孙娟丽出资380万元，孙国奉出资100万元。注册资本增至2,000万元。2008年1月，温州三联将395万元转让予孙国奉、97.5万元予孙国敏、127.5万元予张松满；孙娟丽将380万元转让予张松满；张爱连将400万元转让予孙国敏。</t>
         </is>
       </c>
@@ -638,6 +696,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>2007年12月，三联有限第一次增资1,500万元，温州三联出资620万元，张爱连出资400万元，孙娟丽出资380万元，孙国奉出资100万元。注册资本增至2,000万元。2008年1月，温州三联将395万元转让予孙国奉、97.5万元予孙国敏、127.5万元予张松满；孙娟丽将380万元转让予张松满；张爱连将400万元转让予孙国敏。</t>
         </is>
       </c>
@@ -663,6 +726,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>增资及股权转让</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>2007年12月，三联有限第一次增资1,500万元，温州三联出资620万元，张爱连出资400万元，孙娟丽出资380万元，孙国奉出资100万元。注册资本增至2,000万元。2008年1月，温州三联将395万元转让予孙国奉、97.5万元予孙国敏、127.5万元予张松满；孙娟丽将380万元转让予张松满；张爱连将400万元转让予孙国敏。</t>
         </is>
       </c>
@@ -688,6 +756,16 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>66.50%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>2014年5月，三联有限第二次增资3,000万元，孙国奉出资1,995万元，张松满出资1,005万元。注册资本增至5,000万元。增资后孙国奉66.50%，张松满33.50%。</t>
         </is>
       </c>
@@ -713,6 +791,16 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>33.50%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>2014年5月，三联有限第二次增资3,000万元，孙国奉出资1,995万元，张松满出资1,005万元。注册资本增至5,000万元。增资后孙国奉66.50%，张松满33.50%。</t>
         </is>
       </c>
@@ -738,6 +826,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>2017年2月，三联有限第三次增资1,150万元，由高新同华出资1,150万元。注册资本增至6,150万元。高新同华为私募创业投资基金。</t>
         </is>
       </c>
@@ -760,6 +853,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>2018年10月11日，三联有限召开股东会，同意整体变更设立股份有限公司。截至2018年7月31日，经审计净资产29,828.50万元（调整后），按1:0.2732折股81,500,000股，每股面值1元。发起人为孙国奉、张一衡、孙国敏、孙仁豪、高新同华5名股东。2018年11月26日经芜湖市工商行政管理局核准。</t>
         </is>
       </c>
@@ -782,6 +880,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>2018年10月11日，三联有限召开股东会，同意整体变更设立股份有限公司。截至2018年7月31日，经审计净资产29,828.50万元（调整后），按1:0.2732折股81,500,000股，每股面值1元。发起人为孙国奉、张一衡、孙国敏、孙仁豪、高新同华5名股东。2018年11月26日经芜湖市工商行政管理局核准。</t>
         </is>
       </c>
@@ -804,6 +907,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>2018年10月11日，三联有限召开股东会，同意整体变更设立股份有限公司。截至2018年7月31日，经审计净资产29,828.50万元（调整后），按1:0.2732折股81,500,000股，每股面值1元。发起人为孙国奉、张一衡、孙国敏、孙仁豪、高新同华5名股东。2018年11月26日经芜湖市工商行政管理局核准。</t>
         </is>
       </c>
@@ -826,6 +934,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>2018年10月11日，三联有限召开股东会，同意整体变更设立股份有限公司。截至2018年7月31日，经审计净资产29,828.50万元（调整后），按1:0.2732折股81,500,000股，每股面值1元。发起人为孙国奉、张一衡、孙国敏、孙仁豪、高新同华5名股东。2018年11月26日经芜湖市工商行政管理局核准。</t>
         </is>
       </c>
@@ -847,6 +960,11 @@
         </is>
       </c>
       <c r="G16" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>2018年10月11日，三联有限召开股东会，同意整体变更设立股份有限公司。截至2018年7月31日，经审计净资产29,828.50万元（调整后），按1:0.2732折股81,500,000股，每股面值1元。发起人为孙国奉、张一衡、孙国敏、孙仁豪、高新同华5名股东。2018年11月26日经芜湖市工商行政管理局核准。</t>
         </is>
@@ -863,7 +981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -875,7 +993,10 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -926,6 +1047,21 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>快照序号</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>股东类型</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>原始创始人</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -961,6 +1097,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>2004年6月1日，孙国奉、孙国敏和张松满就设立三联有限签署了股东协议书及公司章程，注册资本500万元，孙国奉以机器设备出资175万元（35%）；孙国敏以货币和机器设备出资162.5万元（32.5%）；张松满以货币和机器设备出资162.5万元（32.5%）。2004年6月18日经芜湖市工商行政管理局核准。</t>
         </is>
       </c>
@@ -996,6 +1147,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>2004年6月1日，孙国奉、孙国敏和张松满就设立三联有限签署了股东协议书及公司章程，注册资本500万元，孙国奉以机器设备出资175万元（35%）；孙国敏以货币和机器设备出资162.5万元（32.5%）；张松满以货币和机器设备出资162.5万元（32.5%）。2004年6月18日经芜湖市工商行政管理局核准。</t>
         </is>
       </c>
@@ -1031,6 +1197,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>2004年6月1日，孙国奉、孙国敏和张松满就设立三联有限签署了股东协议书及公司章程，注册资本500万元，孙国奉以机器设备出资175万元（35%）；孙国敏以货币和机器设备出资162.5万元（32.5%）；张松满以货币和机器设备出资162.5万元（32.5%）。2004年6月18日经芜湖市工商行政管理局核准。</t>
         </is>
       </c>
@@ -1066,6 +1247,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>2014年5月，三联有限第二次增资3,000万元，孙国奉出资1,995万元，张松满出资1,005万元。注册资本增至5,000万元。增资后孙国奉66.50%，张松满33.50%。</t>
         </is>
       </c>
@@ -1100,6 +1296,21 @@
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>自然人</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>2014年5月，三联有限第二次增资3,000万元，孙国奉出资1,995万元，张松满出资1,005万元。注册资本增至5,000万元。增资后孙国奉66.50%，张松满33.50%。</t>
         </is>
@@ -1116,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1290,100 +1501,84 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidence_text</t>
+          <t>event_context</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>str(min=20)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>source_page</t>
+          <t>post_event_total_shares</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>snapshot_date</t>
+          <t>post_event_total_capital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>str(YYYY-MM-DD)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>snapshot_type</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>total_shares</t>
+          <t>subscription_ratio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>float|null</t>
+          <t>str|null</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1391,20 +1586,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>total_capital</t>
+          <t>evidence_text</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>str(min=20)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1414,7 +1613,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>shareholder_name</t>
+          <t>source_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1436,15 +1635,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>shares_held</t>
+          <t>snapshot_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>str(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1454,15 +1657,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>capital_contribution</t>
+          <t>snapshot_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1472,12 +1679,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shareholding_ratio</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>str|null</t>
+          <t>float|null</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1490,433 +1697,269 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>total_capital</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>shareholder_name</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shares_held</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>capital_contribution</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>shareholding_ratio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>str|null</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>snapshot_order</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>int|null</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>shareholder_type_detail</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>is_original_founder</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>yes/no/unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>evidence_text</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>str(min=20)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Cross-Check 结果（相邻时点股本追踪 + 认缴存量对应）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>上一时点</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>当前时点</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>股东名称</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>上一时点持股数
 (万股)</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>上一时点出资额
 (万元注册资本)</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>本次认缴/变化
 (万股)</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>预期变更后
 持股数(万股)</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>PDF披露
 持股数(万股)</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>差额(万股)</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>175.0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>武汉力源信息技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>深圳市云汉电子有限公司</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1926,35 +1969,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1964,35 +2007,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2004,7 +2047,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2016,17 +2059,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2054,21 +2097,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2092,21 +2139,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2118,7 +2169,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2130,17 +2181,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2156,7 +2207,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2168,17 +2219,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2206,17 +2257,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2232,7 +2283,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2244,17 +2295,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2282,17 +2333,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2308,7 +2359,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2320,17 +2371,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2346,7 +2397,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2358,25 +2409,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2388,7 +2435,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2400,17 +2447,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2426,7 +2473,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2438,17 +2485,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2464,7 +2511,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2476,17 +2523,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2514,17 +2561,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2552,17 +2599,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2578,7 +2625,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2590,21 +2637,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2616,7 +2667,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2628,17 +2679,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2666,17 +2717,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2704,17 +2755,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2730,7 +2781,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2742,17 +2793,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2780,17 +2831,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2806,7 +2857,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2879,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2844,7 +2895,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2856,25 +2907,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -2886,7 +2933,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2898,25 +2945,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -2940,25 +2983,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1584.0</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2970,7 +3009,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2982,17 +3021,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3020,25 +3059,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3050,7 +3085,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3062,25 +3097,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3092,7 +3123,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3104,25 +3135,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3134,7 +3161,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3146,17 +3173,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2015-12-03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3172,7 +3199,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3184,25 +3211,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3214,7 +3237,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3226,21 +3249,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3252,33 +3279,37 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -3290,33 +3321,37 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>7412.0</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3328,33 +3363,37 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3366,35 +3405,35 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3415,26 +3454,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1584.0</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -3444,31 +3487,39 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3478,27 +3529,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3512,27 +3567,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3548,7 +3607,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3560,12 +3619,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3586,7 +3645,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3598,17 +3657,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3636,17 +3695,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3674,21 +3733,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -3712,25 +3775,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -3740,11 +3799,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3754,25 +3809,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -3782,11 +3833,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3796,17 +3843,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3820,11 +3867,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3834,17 +3877,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3860,7 +3903,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3872,12 +3915,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3898,7 +3941,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3953,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3948,12 +3991,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3986,25 +4029,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -4014,7 +4053,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4024,21 +4067,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>2022-05-26</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4050,49 +4097,37 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>6999.972</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-0.028</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4100,49 +4135,41 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2999.988</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-0.012</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4150,49 +4177,37 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1499.994</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4200,49 +4215,37 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4250,49 +4253,37 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4300,99 +4291,75 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>5000.0031</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>0.0031</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.0%</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>3000.0012</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4400,49 +4367,37 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2912.5034</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2912.5</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>0.0034</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4450,7 +4405,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4463,34 +4418,34 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2000.0019</t>
+          <t>6999.972</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0019</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -4513,34 +4468,34 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1747.5007</t>
+          <t>2999.988</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1747.5</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -4563,34 +4518,34 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>1499.994</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -4618,29 +4573,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -4668,29 +4623,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>339.999</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -4710,35 +4665,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4746,7 +4705,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4756,35 +4715,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4792,7 +4755,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4802,27 +4765,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4830,7 +4805,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4840,35 +4815,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4876,7 +4855,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4886,27 +4865,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4914,7 +4905,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4924,35 +4915,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4960,7 +4955,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4970,39 +4965,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5010,7 +5005,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5020,39 +5015,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5060,7 +5055,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5072,30 +5067,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -5118,36 +5113,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5156,7 +5147,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5168,32 +5159,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5202,7 +5185,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5214,36 +5197,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>204.0</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5252,7 +5231,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5264,32 +5243,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5298,7 +5269,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5310,40 +5281,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5352,7 +5315,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5364,32 +5327,36 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5398,7 +5365,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5410,30 +5377,30 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -5456,32 +5423,36 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5490,7 +5461,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5502,40 +5473,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5544,7 +5507,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5556,32 +5519,36 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5590,7 +5557,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5602,30 +5569,30 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -5648,37 +5615,33 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5712,20 +5675,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -5758,20 +5721,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5804,20 +5767,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -5850,20 +5813,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -5896,20 +5859,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -5930,39 +5893,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5970,7 +5937,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5980,39 +5947,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6020,7 +5983,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6030,39 +5993,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6070,7 +6029,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6080,39 +6039,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>罗世兵 (认缴→存量)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6120,7 +6075,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6130,39 +6085,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6170,7 +6129,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6180,39 +6139,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6220,7 +6175,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6230,39 +6185,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6270,7 +6221,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6231,11 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>2022-12-19</t>
@@ -6288,31 +6243,31 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6320,7 +6275,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6333,29 +6288,29 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6383,29 +6338,29 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6433,29 +6388,29 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6483,29 +6438,29 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6533,29 +6488,29 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -6583,29 +6538,29 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -6633,29 +6588,29 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -6688,24 +6643,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -6738,24 +6693,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -6777,30 +6732,42 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6808,37 +6775,49 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6846,37 +6825,49 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6884,71 +6875,99 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6956,37 +6975,49 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6994,37 +7025,49 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7032,37 +7075,49 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7070,7 +7125,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7147,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7130,7 +7185,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7168,7 +7223,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7184,7 +7239,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7261,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7229,22 +7284,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7258,31 +7313,27 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7305,22 +7356,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7336,29 +7387,29 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7374,29 +7425,29 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7412,29 +7463,29 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7457,22 +7508,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7495,22 +7546,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7548,7 +7599,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7576,17 +7627,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7602,7 +7653,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7614,17 +7665,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7640,7 +7691,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7652,25 +7703,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -7680,7 +7727,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7690,17 +7741,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -7716,7 +7767,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7728,17 +7779,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -7766,17 +7817,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -7792,7 +7843,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7804,17 +7855,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -7830,7 +7881,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7842,17 +7893,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -7880,21 +7931,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
           <t>2020-02-26</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -7904,51 +7959,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7956,29 +7995,29 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8001,22 +8040,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8032,29 +8071,29 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8070,29 +8109,29 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8108,29 +8147,29 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8146,37 +8185,33 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -8195,30 +8230,26 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8237,34 +8268,42 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>盛祎等15名自然人</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8272,44 +8311,36 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.9%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
@@ -8318,37 +8349,33 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
@@ -8367,37 +8394,29 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
@@ -8418,32 +8437,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
@@ -8452,7 +8467,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8464,23 +8479,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -8506,32 +8521,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
@@ -8552,32 +8559,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
@@ -8598,32 +8597,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
@@ -8632,7 +8627,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8654,22 +8649,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -8678,7 +8669,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8679,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8696,31 +8691,23 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8728,7 +8715,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8725,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8746,7 +8737,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -8756,21 +8747,13 @@
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
         <is>
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8778,7 +8761,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8771,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8796,31 +8783,23 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8828,7 +8807,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8817,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8846,31 +8829,23 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8878,7 +8853,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8863,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8896,31 +8875,23 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8928,7 +8899,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8909,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8946,31 +8921,23 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8978,7 +8945,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8955,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8996,31 +8967,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9028,35 +8987,431 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
           <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 15 条</t>
-        </is>
-      </c>
-    </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 5 条</t>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T14:44:15.747839</t>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 15 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 5 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T15:16:10.930747</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2007,11 +2007,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2031,7 +2027,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2049,7 +2045,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2069,11 +2069,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2085,7 +2089,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2107,15 +2111,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2571,15 +2571,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -2591,7 +2587,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2609,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2629,7 +2625,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2647,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2667,7 +2663,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2685,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2705,7 +2701,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2723,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2743,7 +2739,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2765,11 +2761,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3221,13 +3221,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3263,13 +3263,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3305,13 +3305,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3347,13 +3347,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3389,13 +3389,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3469,13 +3469,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3549,15 +3549,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3569,7 +3565,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3591,11 +3587,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3667,15 +3667,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3687,7 +3683,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3709,11 +3705,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4077,15 +4077,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4097,7 +4093,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4161,11 +4157,15 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4237,11 +4237,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -4251,11 +4255,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4351,15 +4351,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -4369,7 +4365,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5077,14 +5077,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5093,7 +5101,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5115,20 +5123,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -5161,22 +5169,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5207,22 +5207,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5231,7 +5223,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5253,20 +5245,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -5299,14 +5291,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5337,22 +5337,26 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5361,7 +5365,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5383,23 +5387,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>408.0</t>
+          <t>17952.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -5433,26 +5437,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5483,26 +5483,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5511,7 +5507,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5533,22 +5529,26 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5579,26 +5579,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -5607,7 +5603,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5629,22 +5625,26 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5675,30 +5675,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -5707,7 +5699,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5875,22 +5867,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5921,30 +5921,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -5953,7 +5945,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5975,20 +5967,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6021,20 +6013,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -6067,20 +6059,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6113,20 +6105,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -6159,22 +6151,30 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6205,20 +6205,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -6251,20 +6251,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -7979,11 +7979,15 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -7993,11 +7997,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8017,15 +8017,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -8035,7 +8031,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -8531,11 +8531,15 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
@@ -8547,7 +8551,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8573,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -8607,15 +8611,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8649,20 +8649,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -8695,18 +8695,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -8715,7 +8719,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8737,20 +8741,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -8783,20 +8787,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -8829,22 +8833,18 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8875,20 +8875,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -8921,20 +8921,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -8967,20 +8967,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -9404,7 +9404,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T16:09:12.594546</t>
+          <t>生成时间: 2026-06-12T16:30:01.034541</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
+++ b/outputs/week2_excel/001282_三联锻造_三表抽取.xlsx
@@ -1327,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2069,15 +2069,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2089,7 +2085,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2107,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2149,11 +2145,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2685,15 +2685,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -2727,11 +2723,15 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3221,13 +3221,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3263,15 +3263,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3283,7 +3279,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3305,13 +3301,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3347,13 +3343,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3389,11 +3385,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3427,13 +3427,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3469,13 +3469,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3511,15 +3511,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3531,7 +3527,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3553,11 +3549,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3667,11 +3667,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3683,7 +3687,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3709,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3743,15 +3747,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4077,11 +4077,15 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4093,7 +4097,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4115,15 +4119,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4157,13 +4157,13 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10377.0</t>
+          <t>1153.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -4199,11 +4199,15 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -4213,11 +4217,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4313,15 +4313,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -4331,7 +4327,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4412,30 +4412,42 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6999.972</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-0.028</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4443,37 +4455,49 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2999.988</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4481,37 +4505,49 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1499.994</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4519,37 +4555,49 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4557,37 +4605,49 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4595,37 +4655,49 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4633,37 +4705,49 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4671,37 +4755,49 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4709,37 +4805,49 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4747,75 +4855,99 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4823,37 +4955,49 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4861,37 +5005,49 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4899,29 +5055,29 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -4944,29 +5100,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -4975,36 +5139,44 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5013,36 +5185,44 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5058,22 +5238,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -5096,42 +5276,38 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5139,36 +5315,44 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5184,29 +5368,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -5215,35 +5407,47 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>朱绶青</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
@@ -5260,33 +5464,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5295,35 +5503,47 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -5333,35 +5553,47 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
@@ -5371,39 +5603,47 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
@@ -5420,33 +5660,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -5455,42 +5699,42 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5508,33 +5752,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
@@ -5543,42 +5791,42 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -5596,37 +5844,45 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>策星揽月</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -5635,44 +5891,52 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>幸福一期</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -5681,42 +5945,42 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -5734,33 +5998,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -5769,42 +6037,42 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -5822,37 +6090,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -5861,49 +6137,45 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5911,49 +6183,45 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5961,49 +6229,45 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6011,42 +6275,42 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6068,35 +6332,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6118,35 +6382,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6168,35 +6432,35 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6215,24 +6479,2932 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 15 条</t>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 5 条</t>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:00:58.744122</t>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Cheer Rise Consultants Limited</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>史建伟</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>周乃鼎</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>黄学英/刘鸿雁</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>深圳中证投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>厦门富凯海创投资管理有限责任公司</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>盛祎等15名自然人</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>盛祎</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>朱绶青</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>四方股份</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>吴功友(王金林代持)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>牛威(罗永红代持)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>策星九天</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>策星逐日</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>幸福一期</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>策星揽月</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 15 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 5 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T17:05:42.578384</t>
         </is>
       </c>
     </row>
